--- a/Northstar_HealthTech_IAM_Governance_Dashboard_v1.0_Portfolio_Reviewed.xlsx
+++ b/Northstar_HealthTech_IAM_Governance_Dashboard_v1.0_Portfolio_Reviewed.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfbe32ba94cb2433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Definitions" sheetId="2" r:id="R2124bc8fc8c148cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="3" r:id="R9460b512b8a944ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="4" r:id="Ra1fc808f1fa54ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes" sheetId="5" r:id="Ra9a238a03cef426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R139c516ce0e44b93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Definitions" sheetId="2" r:id="Rc653f4b855e5442c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="3" r:id="Rcd8c654fbfc941bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="4" r:id="R0de50d20fe9e4902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes" sheetId="5" r:id="R682832b01ab74828"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -903,7 +903,7 @@
         <x:v>Onboarding timeliness</x:v>
       </x:c>
       <x:c r="I5" s="22" t="str">
-        <x:f>IF(OR(C5="",D5="",E5&lt;&gt;"Verified",F5=""),"Data Incomplete",IF(OR(C5&lt;0,D5&lt;0,C5&gt;D5),"Data Incomplete",IF(D5=0,"N/A",C5/D5)))</x:f>
+        <x:f>IF(OR(B5="",COUNT(C5:D5)&lt;&gt;2,E5&lt;&gt;"Verified",F5="",NOT(ISNUMBER(G5))),"Data Incomplete",IF(OR(C5&lt;0,D5&lt;0,C5&gt;D5,MOD(C5,1)&lt;&gt;0,MOD(D5,1)&lt;&gt;0),"Data Incomplete",IF(D5=0,"N/A",C5/D5)))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -912,7 +912,7 @@
         <x:v>Offboarding compliance</x:v>
       </x:c>
       <x:c r="I6" s="22" t="str">
-        <x:f>IF(OR(C6="",D6="",E6&lt;&gt;"Verified",F6=""),"Data Incomplete",IF(OR(C6&lt;0,D6&lt;0,C6&gt;D6),"Data Incomplete",IF(D6=0,"N/A",C6/D6)))</x:f>
+        <x:f>IF(OR(B6="",COUNT(C6:D6)&lt;&gt;2,E6&lt;&gt;"Verified",F6="",NOT(ISNUMBER(G6))),"Data Incomplete",IF(OR(C6&lt;0,D6&lt;0,C6&gt;D6,MOD(C6,1)&lt;&gt;0,MOD(D6,1)&lt;&gt;0),"Data Incomplete",IF(D6=0,"N/A",C6/D6)))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -921,7 +921,7 @@
         <x:v>Access review completion</x:v>
       </x:c>
       <x:c r="I7" s="22" t="str">
-        <x:f>IF(OR(C7="",D7="",E7&lt;&gt;"Verified",F7=""),"Data Incomplete",IF(OR(C7&lt;0,D7&lt;0,C7&gt;D7),"Data Incomplete",IF(D7=0,"N/A",C7/D7)))</x:f>
+        <x:f>IF(OR(B7="",COUNT(C7:D7)&lt;&gt;2,E7&lt;&gt;"Verified",F7="",NOT(ISNUMBER(G7))),"Data Incomplete",IF(OR(C7&lt;0,D7&lt;0,C7&gt;D7,MOD(C7,1)&lt;&gt;0,MOD(D7,1)&lt;&gt;0),"Data Incomplete",IF(D7=0,"N/A",C7/D7)))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -930,7 +930,7 @@
         <x:v>Revocation timeliness</x:v>
       </x:c>
       <x:c r="I8" s="22" t="str">
-        <x:f>IF(OR(C8="",D8="",E8&lt;&gt;"Verified",F8=""),"Data Incomplete",IF(OR(C8&lt;0,D8&lt;0,C8&gt;D8),"Data Incomplete",IF(D8=0,"N/A",C8/D8)))</x:f>
+        <x:f>IF(OR(B8="",COUNT(C8:D8)&lt;&gt;2,E8&lt;&gt;"Verified",F8="",NOT(ISNUMBER(G8))),"Data Incomplete",IF(OR(C8&lt;0,D8&lt;0,C8&gt;D8,MOD(C8,1)&lt;&gt;0,MOD(D8,1)&lt;&gt;0),"Data Incomplete",IF(D8=0,"N/A",C8/D8)))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -939,7 +939,7 @@
         <x:v>Privileged approval compliance</x:v>
       </x:c>
       <x:c r="I9" s="22" t="str">
-        <x:f>IF(OR(C9="",D9="",E9&lt;&gt;"Verified",F9=""),"Data Incomplete",IF(OR(C9&lt;0,D9&lt;0,C9&gt;D9),"Data Incomplete",IF(D9=0,"N/A",C9/D9)))</x:f>
+        <x:f>IF(OR(B9="",COUNT(C9:D9)&lt;&gt;2,E9&lt;&gt;"Verified",F9="",NOT(ISNUMBER(G9))),"Data Incomplete",IF(OR(C9&lt;0,D9&lt;0,C9&gt;D9,MOD(C9,1)&lt;&gt;0,MOD(D9,1)&lt;&gt;0),"Data Incomplete",IF(D9=0,"N/A",C9/D9)))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -948,7 +948,7 @@
         <x:v>MFA coverage</x:v>
       </x:c>
       <x:c r="I10" s="22" t="str">
-        <x:f>IF(OR(C10="",D10="",E10&lt;&gt;"Verified",F10=""),"Data Incomplete",IF(OR(C10&lt;0,D10&lt;0,C10&gt;D10),"Data Incomplete",IF(D10=0,"N/A",C10/D10)))</x:f>
+        <x:f>IF(OR(B10="",COUNT(C10:D10)&lt;&gt;2,E10&lt;&gt;"Verified",F10="",NOT(ISNUMBER(G10))),"Data Incomplete",IF(OR(C10&lt;0,D10&lt;0,C10&gt;D10,MOD(C10,1)&lt;&gt;0,MOD(D10,1)&lt;&gt;0),"Data Incomplete",IF(D10=0,"N/A",C10/D10)))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -1154,7 +1154,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="83" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -1168,7 +1168,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>v1.0 — Portfolio-reviewed candidate</x:v>
+        <x:v>v1.0 — Portfolio reviewed (educational simulation)</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="35" customHeight="1">
@@ -1216,7 +1216,7 @@
         <x:v>Calculation rule</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>A numeric result requires populated numerator, denominator, Verified status, and evidence reference.</x:v>
+        <x:v>Numeric result requires reporting month, whole-number numerator/denominator, Verified status, evidence reference, and true Excel extraction date. Zero numerator allowed; zero denominator N/A.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="35" customHeight="1">
@@ -1233,6 +1233,22 @@
       </x:c>
       <x:c r="B10" s="24" t="str">
         <x:v>Promoted from draft v0.1 with clearer simulation labeling; no production metrics fabricated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Validation note</x:v>
+      </x:c>
+      <x:c r="B11" s="24" t="str">
+        <x:v>Use real Excel dates in Extraction date; missing dates/months must produce Data Incomplete.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Verification recommendation</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
+        <x:v>Before publication, test 0/10, 4/5, blank reporting period/date, and 0/0 in desktop Excel; no production metrics claimed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Northstar_HealthTech_IAM_Governance_Dashboard_v1.0_Portfolio_Reviewed.xlsx
+++ b/Northstar_HealthTech_IAM_Governance_Dashboard_v1.0_Portfolio_Reviewed.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R139c516ce0e44b93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Definitions" sheetId="2" r:id="Rc653f4b855e5442c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="3" r:id="Rcd8c654fbfc941bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="4" r:id="R0de50d20fe9e4902"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes" sheetId="5" r:id="R682832b01ab74828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re3ba4022a6e740de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Definitions" sheetId="2" r:id="R34d73167dc274a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="3" r:id="R21d75f088c444961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="4" r:id="R3aabeb3b8b274ee6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes" sheetId="5" r:id="R4a1d0f442d5549ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,10 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0%"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="203" formatCode="mmm yyyy"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -101,7 +102,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -152,6 +153,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -574,7 +576,8 @@
       <x:c r="A12" t="str">
         <x:v>Reporting period</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B12" s="36" t="str">
+        <x:f>IF(COUNTIF('Data Entry'!B5:B10,"&lt;&gt;")=0,"Not entered",IF(COUNTIF('Data Entry'!B5:B10,"&lt;&gt;")&lt;6,"Data Incomplete",IF(COUNTIF('Data Entry'!B5:B10,'Data Entry'!B5)=6,'Data Entry'!B5,"Mixed reporting months")))</x:f>
         <x:v>Not entered</x:v>
       </x:c>
     </x:row>
@@ -1243,12 +1246,20 @@
         <x:v>Use real Excel dates in Extraction date; missing dates/months must produce Data Incomplete.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>Verification recommendation</x:v>
       </x:c>
       <x:c r="B12" s="24" t="str">
-        <x:v>Before publication, test 0/10, 4/5, blank reporting period/date, and 0/0 in desktop Excel; no production metrics claimed.</x:v>
+        <x:v>Review status as of 28 October 2026: local formula checks included 0/10, 4/5, missing month/extraction date, and 0/0. Desktop Excel execution has not been independently confirmed; validate there before relying on future populated results.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>Reporting period display</x:v>
+      </x:c>
+      <x:c r="B13" s="24" t="str">
+        <x:v>Dashboard!B12 derives the month from Data Entry!B5:B10; all six must be supplied and match. Blank, partial, or mixed months are flagged. KPI calculations continue to require Verified evidence and dates.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Northstar_HealthTech_IAM_Governance_Dashboard_v1.0_Portfolio_Reviewed.xlsx
+++ b/Northstar_HealthTech_IAM_Governance_Dashboard_v1.0_Portfolio_Reviewed.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re3ba4022a6e740de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Definitions" sheetId="2" r:id="R34d73167dc274a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="3" r:id="R21d75f088c444961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="4" r:id="R3aabeb3b8b274ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes" sheetId="5" r:id="R4a1d0f442d5549ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf466b09bacd241c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Definitions" sheetId="2" r:id="R584a1443b6f04ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="3" r:id="R4625ce7682ef4b88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="4" r:id="R2e80333dab904b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Notes" sheetId="5" r:id="Rd586b7afbdb04f40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -418,7 +418,7 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:f>'Data Entry'!I5</x:f>
+        <x:f>IF(OR($B$12="Mixed reporting months",$B$12="Data Incomplete",$B$12="Not entered"),"Data Incomplete",'Data Entry'!I5)</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
       <x:c r="D5" t="str">
@@ -445,7 +445,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="16" t="str">
-        <x:f>'Data Entry'!I6</x:f>
+        <x:f>IF(OR($B$12="Mixed reporting months",$B$12="Data Incomplete",$B$12="Not entered"),"Data Incomplete",'Data Entry'!I6)</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
       <x:c r="D6" t="str">
@@ -472,7 +472,7 @@
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str">
-        <x:f>'Data Entry'!I7</x:f>
+        <x:f>IF(OR($B$12="Mixed reporting months",$B$12="Data Incomplete",$B$12="Not entered"),"Data Incomplete",'Data Entry'!I7)</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
       <x:c r="D7" t="str">
@@ -499,7 +499,7 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:f>'Data Entry'!I8</x:f>
+        <x:f>IF(OR($B$12="Mixed reporting months",$B$12="Data Incomplete",$B$12="Not entered"),"Data Incomplete",'Data Entry'!I8)</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
       <x:c r="D8" t="str">
@@ -526,7 +526,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="16" t="str">
-        <x:f>'Data Entry'!I9</x:f>
+        <x:f>IF(OR($B$12="Mixed reporting months",$B$12="Data Incomplete",$B$12="Not entered"),"Data Incomplete",'Data Entry'!I9)</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
       <x:c r="D9" t="str">
@@ -553,7 +553,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="16" t="str">
-        <x:f>'Data Entry'!I10</x:f>
+        <x:f>IF(OR($B$12="Mixed reporting months",$B$12="Data Incomplete",$B$12="Not entered"),"Data Incomplete",'Data Entry'!I10)</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
       <x:c r="D10" t="str">
@@ -577,7 +577,7 @@
         <x:v>Reporting period</x:v>
       </x:c>
       <x:c r="B12" s="36" t="str">
-        <x:f>IF(COUNTIF('Data Entry'!B5:B10,"&lt;&gt;")=0,"Not entered",IF(COUNTIF('Data Entry'!B5:B10,"&lt;&gt;")&lt;6,"Data Incomplete",IF(COUNTIF('Data Entry'!B5:B10,'Data Entry'!B5)=6,'Data Entry'!B5,"Mixed reporting months")))</x:f>
+        <x:f>IF(COUNTIF('Data Entry'!B5:B10,"&lt;&gt;")=0,"Not entered",IF(COUNTIF('Data Entry'!B5:B10,"&lt;&gt;")&lt;6,"Data Incomplete",IF(COUNTIF('Data Entry'!B5:B10,'Data Entry'!B5)&lt;&gt;6,"Mixed reporting months",IFERROR(IF(AND(LEN('Data Entry'!B5)=7,MID('Data Entry'!B5,5,1)="-",TEXT(DATEVALUE('Data Entry'!B5&amp;"-01"),"yyyy-mm")='Data Entry'!B5),'Data Entry'!B5,"Data Incomplete"),"Data Incomplete"))))</x:f>
         <x:v>Not entered</x:v>
       </x:c>
     </x:row>
@@ -820,6 +820,22 @@
       </x:c>
       <x:c r="B16" t="str">
         <x:v>Active unauthorized access must be escalated immediately</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Consolidated period gate</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>All six reporting months must match and use YYYY-MM before any KPI actual may be displayed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Extraction date window</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Month-end through the following month-end inclusive; invalid numeric dates are rejected.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -906,7 +922,7 @@
         <x:v>Onboarding timeliness</x:v>
       </x:c>
       <x:c r="I5" s="22" t="str">
-        <x:f>IF(OR(B5="",COUNT(C5:D5)&lt;&gt;2,E5&lt;&gt;"Verified",F5="",NOT(ISNUMBER(G5))),"Data Incomplete",IF(OR(C5&lt;0,D5&lt;0,C5&gt;D5,MOD(C5,1)&lt;&gt;0,MOD(D5,1)&lt;&gt;0),"Data Incomplete",IF(D5=0,"N/A",C5/D5)))</x:f>
+        <x:f>IF(OR(Dashboard!$B$12="Not entered",Dashboard!$B$12="Mixed reporting months",Dashboard!$B$12="Data Incomplete",B5="",COUNT(C5:D5)&lt;&gt;2,E5&lt;&gt;"Verified",F5="",NOT(ISNUMBER(G5))),"Data Incomplete",IFERROR(IF(OR(LEN(B5)&lt;&gt;7,MID(B5,5,1)&lt;&gt;"-",TEXT(IFERROR(DATEVALUE(B5&amp;"-01"),0),"yyyy-mm")&lt;&gt;B5,G5&lt;&gt;INT(G5),G5&lt;EOMONTH(IFERROR(DATEVALUE(B5&amp;"-01"),0),0),G5&gt;EOMONTH(IFERROR(DATEVALUE(B5&amp;"-01"),0),1),C5&lt;0,D5&lt;0,C5&gt;D5,MOD(C5,1)&lt;&gt;0,MOD(D5,1)&lt;&gt;0),"Data Incomplete",IF(D5=0,"N/A",C5/D5)),"Data Incomplete"))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -915,7 +931,7 @@
         <x:v>Offboarding compliance</x:v>
       </x:c>
       <x:c r="I6" s="22" t="str">
-        <x:f>IF(OR(B6="",COUNT(C6:D6)&lt;&gt;2,E6&lt;&gt;"Verified",F6="",NOT(ISNUMBER(G6))),"Data Incomplete",IF(OR(C6&lt;0,D6&lt;0,C6&gt;D6,MOD(C6,1)&lt;&gt;0,MOD(D6,1)&lt;&gt;0),"Data Incomplete",IF(D6=0,"N/A",C6/D6)))</x:f>
+        <x:f>IF(OR(Dashboard!$B$12="Not entered",Dashboard!$B$12="Mixed reporting months",Dashboard!$B$12="Data Incomplete",B6="",COUNT(C6:D6)&lt;&gt;2,E6&lt;&gt;"Verified",F6="",NOT(ISNUMBER(G6))),"Data Incomplete",IFERROR(IF(OR(LEN(B6)&lt;&gt;7,MID(B6,5,1)&lt;&gt;"-",TEXT(IFERROR(DATEVALUE(B6&amp;"-01"),0),"yyyy-mm")&lt;&gt;B6,G6&lt;&gt;INT(G6),G6&lt;EOMONTH(IFERROR(DATEVALUE(B6&amp;"-01"),0),0),G6&gt;EOMONTH(IFERROR(DATEVALUE(B6&amp;"-01"),0),1),C6&lt;0,D6&lt;0,C6&gt;D6,MOD(C6,1)&lt;&gt;0,MOD(D6,1)&lt;&gt;0),"Data Incomplete",IF(D6=0,"N/A",C6/D6)),"Data Incomplete"))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -924,7 +940,7 @@
         <x:v>Access review completion</x:v>
       </x:c>
       <x:c r="I7" s="22" t="str">
-        <x:f>IF(OR(B7="",COUNT(C7:D7)&lt;&gt;2,E7&lt;&gt;"Verified",F7="",NOT(ISNUMBER(G7))),"Data Incomplete",IF(OR(C7&lt;0,D7&lt;0,C7&gt;D7,MOD(C7,1)&lt;&gt;0,MOD(D7,1)&lt;&gt;0),"Data Incomplete",IF(D7=0,"N/A",C7/D7)))</x:f>
+        <x:f>IF(OR(Dashboard!$B$12="Not entered",Dashboard!$B$12="Mixed reporting months",Dashboard!$B$12="Data Incomplete",B7="",COUNT(C7:D7)&lt;&gt;2,E7&lt;&gt;"Verified",F7="",NOT(ISNUMBER(G7))),"Data Incomplete",IFERROR(IF(OR(LEN(B7)&lt;&gt;7,MID(B7,5,1)&lt;&gt;"-",TEXT(IFERROR(DATEVALUE(B7&amp;"-01"),0),"yyyy-mm")&lt;&gt;B7,G7&lt;&gt;INT(G7),G7&lt;EOMONTH(IFERROR(DATEVALUE(B7&amp;"-01"),0),0),G7&gt;EOMONTH(IFERROR(DATEVALUE(B7&amp;"-01"),0),1),C7&lt;0,D7&lt;0,C7&gt;D7,MOD(C7,1)&lt;&gt;0,MOD(D7,1)&lt;&gt;0),"Data Incomplete",IF(D7=0,"N/A",C7/D7)),"Data Incomplete"))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -933,7 +949,7 @@
         <x:v>Revocation timeliness</x:v>
       </x:c>
       <x:c r="I8" s="22" t="str">
-        <x:f>IF(OR(B8="",COUNT(C8:D8)&lt;&gt;2,E8&lt;&gt;"Verified",F8="",NOT(ISNUMBER(G8))),"Data Incomplete",IF(OR(C8&lt;0,D8&lt;0,C8&gt;D8,MOD(C8,1)&lt;&gt;0,MOD(D8,1)&lt;&gt;0),"Data Incomplete",IF(D8=0,"N/A",C8/D8)))</x:f>
+        <x:f>IF(OR(Dashboard!$B$12="Not entered",Dashboard!$B$12="Mixed reporting months",Dashboard!$B$12="Data Incomplete",B8="",COUNT(C8:D8)&lt;&gt;2,E8&lt;&gt;"Verified",F8="",NOT(ISNUMBER(G8))),"Data Incomplete",IFERROR(IF(OR(LEN(B8)&lt;&gt;7,MID(B8,5,1)&lt;&gt;"-",TEXT(IFERROR(DATEVALUE(B8&amp;"-01"),0),"yyyy-mm")&lt;&gt;B8,G8&lt;&gt;INT(G8),G8&lt;EOMONTH(IFERROR(DATEVALUE(B8&amp;"-01"),0),0),G8&gt;EOMONTH(IFERROR(DATEVALUE(B8&amp;"-01"),0),1),C8&lt;0,D8&lt;0,C8&gt;D8,MOD(C8,1)&lt;&gt;0,MOD(D8,1)&lt;&gt;0),"Data Incomplete",IF(D8=0,"N/A",C8/D8)),"Data Incomplete"))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -942,7 +958,7 @@
         <x:v>Privileged approval compliance</x:v>
       </x:c>
       <x:c r="I9" s="22" t="str">
-        <x:f>IF(OR(B9="",COUNT(C9:D9)&lt;&gt;2,E9&lt;&gt;"Verified",F9="",NOT(ISNUMBER(G9))),"Data Incomplete",IF(OR(C9&lt;0,D9&lt;0,C9&gt;D9,MOD(C9,1)&lt;&gt;0,MOD(D9,1)&lt;&gt;0),"Data Incomplete",IF(D9=0,"N/A",C9/D9)))</x:f>
+        <x:f>IF(OR(Dashboard!$B$12="Not entered",Dashboard!$B$12="Mixed reporting months",Dashboard!$B$12="Data Incomplete",B9="",COUNT(C9:D9)&lt;&gt;2,E9&lt;&gt;"Verified",F9="",NOT(ISNUMBER(G9))),"Data Incomplete",IFERROR(IF(OR(LEN(B9)&lt;&gt;7,MID(B9,5,1)&lt;&gt;"-",TEXT(IFERROR(DATEVALUE(B9&amp;"-01"),0),"yyyy-mm")&lt;&gt;B9,G9&lt;&gt;INT(G9),G9&lt;EOMONTH(IFERROR(DATEVALUE(B9&amp;"-01"),0),0),G9&gt;EOMONTH(IFERROR(DATEVALUE(B9&amp;"-01"),0),1),C9&lt;0,D9&lt;0,C9&gt;D9,MOD(C9,1)&lt;&gt;0,MOD(D9,1)&lt;&gt;0),"Data Incomplete",IF(D9=0,"N/A",C9/D9)),"Data Incomplete"))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -951,7 +967,7 @@
         <x:v>MFA coverage</x:v>
       </x:c>
       <x:c r="I10" s="22" t="str">
-        <x:f>IF(OR(B10="",COUNT(C10:D10)&lt;&gt;2,E10&lt;&gt;"Verified",F10="",NOT(ISNUMBER(G10))),"Data Incomplete",IF(OR(C10&lt;0,D10&lt;0,C10&gt;D10,MOD(C10,1)&lt;&gt;0,MOD(D10,1)&lt;&gt;0),"Data Incomplete",IF(D10=0,"N/A",C10/D10)))</x:f>
+        <x:f>IF(OR(Dashboard!$B$12="Not entered",Dashboard!$B$12="Mixed reporting months",Dashboard!$B$12="Data Incomplete",B10="",COUNT(C10:D10)&lt;&gt;2,E10&lt;&gt;"Verified",F10="",NOT(ISNUMBER(G10))),"Data Incomplete",IFERROR(IF(OR(LEN(B10)&lt;&gt;7,MID(B10,5,1)&lt;&gt;"-",TEXT(IFERROR(DATEVALUE(B10&amp;"-01"),0),"yyyy-mm")&lt;&gt;B10,G10&lt;&gt;INT(G10),G10&lt;EOMONTH(IFERROR(DATEVALUE(B10&amp;"-01"),0),0),G10&gt;EOMONTH(IFERROR(DATEVALUE(B10&amp;"-01"),0),1),C10&lt;0,D10&lt;0,C10&gt;D10,MOD(C10,1)&lt;&gt;0,MOD(D10,1)&lt;&gt;0),"Data Incomplete",IF(D10=0,"N/A",C10/D10)),"Data Incomplete"))</x:f>
         <x:v>Data Incomplete</x:v>
       </x:c>
     </x:row>
@@ -1262,6 +1278,30 @@
         <x:v>Dashboard!B12 derives the month from Data Entry!B5:B10; all six must be supplied and match. Blank, partial, or mixed months are flagged. KPI calculations continue to require Verified evidence and dates.</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Dashboard safety gate</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>A mixed, missing, or malformed reporting month blocks all six KPI actuals and target statuses; no consolidated monthly result is published.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Extraction-date rule</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Extraction date must be a whole-number Excel date between the last day of the reporting month and the last day of the following month (inclusive). Month input is text YYYY-MM.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Validation status</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Formula logic revised for portfolio review. Validate populated scenarios in desktop Excel before relying on operational reporting; no real organizational KPI data is asserted.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
